--- a/results/run_complet_annee_dyn/metrics_pysr.xlsx
+++ b/results/run_complet_annee_dyn/metrics_pysr.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,6 +591,146 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>PySR déroulement 24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PySR_model</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.08702162313406853</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2949942764428973</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1270727855443836</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.539199911982021</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01167575725937417</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9913063309951027</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.339230988559739</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0868852998264887</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2947631249435531</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0004642616053827394</v>
+      </c>
+      <c r="L4" t="n">
+        <v>55.601218900003</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03388450000056764</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PySR pour l'année airport, 15 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PySR_model</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10.09432770565318</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.177157173583513</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.404927297433377</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15.78625887374886</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6253426667326188</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.008483088466318067</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14.43545184341898</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.703274254816915</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.115007906060098</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0005624343362038191</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>179.7575221000006</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PySR déroulement 24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PySR_model</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.09168985306466174</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3028033240647496</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1227562912885819</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.69792756731034</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.003672412587200015</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9908399636211823</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.374682925771638</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.00829239847271</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.473062977253139</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>16.60744030000205</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.007579400000395253</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PySR pour l'année airport, 15 min</t>
         </is>
       </c>
     </row>
